--- a/To Add v2/00 Things To Add.xlsx
+++ b/To Add v2/00 Things To Add.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Danakil_KiCad_DB\To Add v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DB5800-6D8A-4F05-851F-AE58A0DE31D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DCAE9D-65FF-4EED-8672-7CC368A87C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="7725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -736,7 +736,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -864,7 +864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -939,6 +939,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1363,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AE157"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.08984375" customWidth="1"/>
     <col min="4" max="4" width="27.54296875" style="9" bestFit="1" customWidth="1"/>
@@ -1388,17 +1389,17 @@
     <col min="32" max="32" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31">
+    <row r="1" spans="2:31" x14ac:dyDescent="0.35">
       <c r="I1"/>
       <c r="P1"/>
       <c r="S1"/>
     </row>
-    <row r="2" spans="2:31">
+    <row r="2" spans="2:31" x14ac:dyDescent="0.35">
       <c r="I2"/>
       <c r="P2"/>
       <c r="S2"/>
     </row>
-    <row r="3" spans="2:31">
+    <row r="3" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B3" s="17" t="s">
         <v>48</v>
       </c>
@@ -1416,7 +1417,7 @@
       <c r="P3"/>
       <c r="S3"/>
     </row>
-    <row r="4" spans="2:31">
+    <row r="4" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B4" s="18"/>
       <c r="C4" s="25"/>
       <c r="D4" s="9" t="s">
@@ -1430,7 +1431,7 @@
       <c r="P4"/>
       <c r="S4"/>
     </row>
-    <row r="5" spans="2:31">
+    <row r="5" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B5" s="18"/>
       <c r="C5" s="25"/>
       <c r="D5" s="9" t="s">
@@ -1473,7 +1474,7 @@
         <v>27.397260273972602</v>
       </c>
     </row>
-    <row r="6" spans="2:31">
+    <row r="6" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B6" s="18"/>
       <c r="C6" s="25"/>
       <c r="D6" s="9" t="s">
@@ -1490,7 +1491,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="2:31">
+    <row r="7" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B7" s="18"/>
       <c r="C7" s="26"/>
       <c r="D7" s="11" t="s">
@@ -1504,7 +1505,7 @@
       <c r="P7"/>
       <c r="S7"/>
     </row>
-    <row r="8" spans="2:31">
+    <row r="8" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B8" s="18"/>
       <c r="C8" s="27" t="s">
         <v>144</v>
@@ -1523,7 +1524,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:31">
+    <row r="9" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B9" s="18"/>
       <c r="C9" s="28"/>
       <c r="D9" s="9" t="s">
@@ -1548,7 +1549,7 @@
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
     </row>
-    <row r="10" spans="2:31">
+    <row r="10" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B10" s="18"/>
       <c r="C10" s="29"/>
       <c r="D10" s="11" t="s">
@@ -1589,7 +1590,7 @@
       <c r="AD10" s="21"/>
       <c r="AE10" s="21"/>
     </row>
-    <row r="11" spans="2:31">
+    <row r="11" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B11" s="18"/>
       <c r="C11" s="24" t="s">
         <v>13</v>
@@ -1674,7 +1675,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:31">
+    <row r="12" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B12" s="18"/>
       <c r="C12" s="25"/>
       <c r="D12" s="9" t="s">
@@ -1754,7 +1755,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:31">
+    <row r="13" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B13" s="18"/>
       <c r="C13" s="26"/>
       <c r="D13" s="11" t="s">
@@ -1766,16 +1767,16 @@
       </c>
       <c r="H13" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Sensors - Temperature - Digital</v>
+        <v>ICs - Interface  - Analog Switch</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="J13" t="s">
-        <v>212</v>
+        <v>119</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="P13" s="6" t="b">
         <v>0</v>
@@ -1787,19 +1788,19 @@
         <v>0</v>
       </c>
       <c r="S13" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
       </c>
       <c r="U13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="b">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X13" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
@@ -1807,15 +1808,15 @@
       </c>
       <c r="Y13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Sensors - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Temperature - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Digital</v>
+        <v>Analog Switch</v>
       </c>
       <c r="AB13" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1834,7 +1835,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:31">
+    <row r="14" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B14" s="18"/>
       <c r="C14" s="24" t="s">
         <v>16</v>
@@ -1844,57 +1845,60 @@
       </c>
       <c r="E14" s="13">
         <f>COUNTIF(W12:W9999,"=0")</f>
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H14" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Voltage References - General Purpose</v>
+        <v>Sensors - Temperature - Digital</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="J14" t="s">
-        <v>222</v>
+        <v>212</v>
+      </c>
+      <c r="K14" t="s">
+        <v>98</v>
       </c>
       <c r="P14" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="5" t="b">
         <v>1</v>
       </c>
       <c r="T14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="b">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Voltage References - </v>
+        <v xml:space="preserve">Sensors - </v>
       </c>
       <c r="Z14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>General Purpose</v>
+        <v xml:space="preserve">Temperature - </v>
       </c>
       <c r="AA14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AB14" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1913,7 +1917,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="2:31">
+    <row r="15" spans="2:31" x14ac:dyDescent="0.35">
       <c r="B15" s="18"/>
       <c r="C15" s="25"/>
       <c r="D15" s="16" t="s">
@@ -1921,60 +1925,60 @@
       </c>
       <c r="E15" s="14">
         <f>COUNTIF(W12:W9999,"&gt;0")</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H15" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Zener</v>
+        <v>ICs - Memory - SD Card</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="J15" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="K15" t="s">
-        <v>221</v>
+        <v>112</v>
       </c>
       <c r="P15" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="b">
         <v>1</v>
       </c>
-      <c r="V15" t="s">
-        <v>184</v>
+      <c r="V15" t="b">
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Diodes - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Zener</v>
+        <v>SD Card</v>
       </c>
       <c r="AB15" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -1993,67 +1997,67 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="2:31">
+    <row r="16" spans="2:31" x14ac:dyDescent="0.35">
       <c r="C16" s="25"/>
       <c r="D16" s="9" t="s">
         <v>148</v>
       </c>
       <c r="E16" s="14" cm="1">
         <f t="array" ref="E16">SUM(IF(W12:W9999 &gt; 0,X12:X9999,0))/COUNTIF(W12:W9999,"&gt;0")</f>
-        <v>14.285714285714285</v>
+        <v>50</v>
       </c>
       <c r="H16" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Transformer - Power - PCB Mount</v>
+        <v>ICs - Analog - ADC</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K16" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="P16" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V16" t="s">
+        <v>184</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Transformer - </v>
+        <v xml:space="preserve">ICs - </v>
       </c>
       <c r="Z16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v xml:space="preserve">Analog - </v>
       </c>
       <c r="AA16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>PCB Mount</v>
+        <v>ADC</v>
       </c>
       <c r="AB16" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2072,7 +2076,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:31">
+    <row r="17" spans="3:31" x14ac:dyDescent="0.35">
       <c r="C17" s="25"/>
       <c r="D17" s="9" t="s">
         <v>150</v>
@@ -2083,56 +2087,53 @@
       </c>
       <c r="H17" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Transformer - Power - Chasis Mount</v>
+        <v>Connectors - Test Points</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="J17" t="s">
-        <v>88</v>
-      </c>
-      <c r="K17" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
       <c r="P17" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="b">
-        <v>0</v>
-      </c>
-      <c r="V17" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="V17" t="s">
+        <v>184</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Transformer - </v>
+        <v xml:space="preserve">Connectors - </v>
       </c>
       <c r="Z17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>Test Points</v>
       </c>
       <c r="AA17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Chasis Mount</v>
+        <v/>
       </c>
       <c r="AB17" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -2151,7 +2152,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:31">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.35">
       <c r="D18" s="9" t="s">
         <v>178</v>
       </c>
@@ -2161,2205 +2162,2193 @@
       </c>
       <c r="H18" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Connectors - Terminal Blocks - Wire to Board</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" t="s">
+        <v>61</v>
+      </c>
+      <c r="K18" t="s">
+        <v>215</v>
+      </c>
+      <c r="P18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="b">
+        <v>1</v>
+      </c>
+      <c r="U18" t="b">
+        <v>1</v>
+      </c>
+      <c r="V18" t="s">
+        <v>184</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>85.714285714285708</v>
+      </c>
+      <c r="Y18" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Connectors - </v>
+      </c>
+      <c r="Z18" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Terminal Blocks - </v>
+      </c>
+      <c r="AA18" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>Wire to Board</v>
+      </c>
+      <c r="AB18" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC18" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD18" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE18" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H19" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Connectors - SD Card Socket</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" t="s">
+        <v>56</v>
+      </c>
+      <c r="P19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="s">
+        <v>184</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>85.714285714285708</v>
+      </c>
+      <c r="Y19" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Connectors - </v>
+      </c>
+      <c r="Z19" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v>SD Card Socket</v>
+      </c>
+      <c r="AA19" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB19" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC19" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD19" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE19" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H20" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Voltage References - General Purpose</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J20" t="s">
+        <v>222</v>
+      </c>
+      <c r="P20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>85.714285714285708</v>
+      </c>
+      <c r="Y20" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Voltage References - </v>
+      </c>
+      <c r="Z20" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v>General Purpose</v>
+      </c>
+      <c r="AA20" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB20" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD20" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE20" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H21" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Discreet - Diodes - Zener</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J21" t="s">
+        <v>90</v>
+      </c>
+      <c r="K21" t="s">
+        <v>221</v>
+      </c>
+      <c r="P21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" t="s">
+        <v>184</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>85.714285714285708</v>
+      </c>
+      <c r="Y21" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Discreet - </v>
+      </c>
+      <c r="Z21" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Diodes - </v>
+      </c>
+      <c r="AA21" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>Zener</v>
+      </c>
+      <c r="AB21" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC21" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD21" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE21" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H22" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Transformer - Power - PCB Mount</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" t="s">
+        <v>88</v>
+      </c>
+      <c r="K22" t="s">
+        <v>69</v>
+      </c>
+      <c r="P22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Transformer - </v>
+      </c>
+      <c r="Z22" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Power - </v>
+      </c>
+      <c r="AA22" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>PCB Mount</v>
+      </c>
+      <c r="AB22" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC22" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD22" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE22" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H23" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Transformer - Power - Chasis Mount</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" t="s">
+        <v>88</v>
+      </c>
+      <c r="K23" t="s">
+        <v>86</v>
+      </c>
+      <c r="P23" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Transformer - </v>
+      </c>
+      <c r="Z23" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Power - </v>
+      </c>
+      <c r="AA23" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>Chasis Mount</v>
+      </c>
+      <c r="AB23" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC23" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD23" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE23" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H24" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Thermal - Tape</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J24" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="P18" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" t="b">
-        <v>0</v>
-      </c>
-      <c r="S18" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18" t="b">
-        <v>0</v>
-      </c>
-      <c r="V18" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y18" t="str">
+      <c r="P24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Thermal - </v>
       </c>
-      <c r="Z18" t="str">
+      <c r="Z24" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Tape</v>
       </c>
-      <c r="AA18" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB18" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC18" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD18" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE18" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="3:31">
-      <c r="H19" t="str">
+      <c r="AA24" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB24" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC24" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD24" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE24" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H25" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Thermal - Paste</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J25" t="s">
         <v>218</v>
       </c>
-      <c r="P19" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="b">
-        <v>0</v>
-      </c>
-      <c r="R19" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T19" t="b">
-        <v>0</v>
-      </c>
-      <c r="U19" t="b">
-        <v>0</v>
-      </c>
-      <c r="V19" t="b">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19" s="6">
+      <c r="P25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>14.285714285714285</v>
       </c>
-      <c r="Y19" t="str">
+      <c r="Y25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Thermal - </v>
       </c>
-      <c r="Z19" t="str">
+      <c r="Z25" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Paste</v>
       </c>
-      <c r="AA19" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB19" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC19" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD19" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE19" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="3:31">
-      <c r="H20" t="str">
+      <c r="AA25" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB25" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC25" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD25" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE25" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H26" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Thermal - Glue</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J26" t="s">
         <v>219</v>
       </c>
-      <c r="P20" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="b">
-        <v>0</v>
-      </c>
-      <c r="R20" t="b">
-        <v>0</v>
-      </c>
-      <c r="S20" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T20" t="b">
-        <v>0</v>
-      </c>
-      <c r="U20" t="b">
-        <v>0</v>
-      </c>
-      <c r="V20" t="b">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y20" t="str">
+      <c r="P26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Thermal - </v>
       </c>
-      <c r="Z20" t="str">
+      <c r="Z26" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Glue</v>
       </c>
-      <c r="AA20" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB20" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC20" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD20" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE20" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="3:31">
-      <c r="H21" t="str">
+      <c r="AA26" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB26" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC26" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD26" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE26" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H27" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Touch Sensor - Capacitive</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I27" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J27" t="s">
         <v>157</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K27" t="s">
         <v>158</v>
       </c>
-      <c r="P21" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="b">
-        <v>0</v>
-      </c>
-      <c r="R21" t="b">
-        <v>0</v>
-      </c>
-      <c r="S21" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21" t="b">
-        <v>0</v>
-      </c>
-      <c r="V21" t="b">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y21" t="str">
+      <c r="P27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Sensors - </v>
       </c>
-      <c r="Z21" t="str">
+      <c r="Z27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Touch Sensor - </v>
       </c>
-      <c r="AA21" t="str">
+      <c r="AA27" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>Capacitive</v>
       </c>
-      <c r="AB21" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC21" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD21" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE21" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="3:31">
-      <c r="H22" t="str">
+      <c r="AB27" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC27" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD27" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE27" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H28" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Temperature - RTDs</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I28" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J28" t="s">
         <v>212</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K28" t="s">
         <v>213</v>
       </c>
-      <c r="P22" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="b">
-        <v>0</v>
-      </c>
-      <c r="R22" t="b">
-        <v>0</v>
-      </c>
-      <c r="S22" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" t="b">
-        <v>0</v>
-      </c>
-      <c r="U22" t="b">
-        <v>0</v>
-      </c>
-      <c r="V22" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-      <c r="X22" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y22" t="str">
+      <c r="P28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Sensors - </v>
       </c>
-      <c r="Z22" t="str">
+      <c r="Z28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Temperature - </v>
       </c>
-      <c r="AA22" t="str">
+      <c r="AA28" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>RTDs</v>
       </c>
-      <c r="AB22" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC22" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD22" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE22" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="3:31">
-      <c r="H23" t="str">
+      <c r="AB28" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC28" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD28" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE28" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H29" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Humidity</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I29" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J29" t="s">
         <v>214</v>
       </c>
-      <c r="P23" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>0</v>
-      </c>
-      <c r="R23" t="b">
-        <v>0</v>
-      </c>
-      <c r="S23" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T23" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23" t="b">
-        <v>0</v>
-      </c>
-      <c r="V23" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y23" t="str">
+      <c r="P29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Sensors - </v>
       </c>
-      <c r="Z23" t="str">
+      <c r="Z29" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Humidity</v>
       </c>
-      <c r="AA23" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB23" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC23" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD23" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE23" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="3:31">
-      <c r="H24" t="str">
+      <c r="AA29" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB29" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC29" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD29" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE29" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H30" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Sensors - Capacitance To Digital</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I30" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J30" s="30" t="s">
         <v>211</v>
       </c>
-      <c r="P24" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
-      <c r="R24" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T24" t="b">
-        <v>0</v>
-      </c>
-      <c r="U24" t="b">
-        <v>0</v>
-      </c>
-      <c r="V24" t="b">
-        <v>0</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
-      </c>
-      <c r="X24" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y24" t="str">
+      <c r="P30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Sensors - </v>
       </c>
-      <c r="Z24" t="str">
+      <c r="Z30" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Capacitance To Digital</v>
       </c>
-      <c r="AA24" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB24" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC24" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD24" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE24" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="3:31">
-      <c r="H25" t="str">
+      <c r="AA30" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB30" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC30" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD30" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE30" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H31" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Resistors - Single - Through Hole</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J31" t="s">
         <v>43</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K31" t="s">
         <v>52</v>
       </c>
-      <c r="P25" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="b">
-        <v>0</v>
-      </c>
-      <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U25" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V25" t="b">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y25" t="str">
+      <c r="P31" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Resistors - </v>
       </c>
-      <c r="Z25" t="str">
+      <c r="Z31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Single - </v>
       </c>
-      <c r="AA25" t="str">
+      <c r="AA31" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>Through Hole</v>
       </c>
-      <c r="AB25" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC25" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD25" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE25" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="3:31">
-      <c r="H26" t="str">
+      <c r="AB31" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC31" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD31" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE31" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.35">
+      <c r="H32" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Resistors - Network</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I32" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J32" t="s">
         <v>51</v>
       </c>
-      <c r="P26" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="b">
-        <v>0</v>
-      </c>
-      <c r="R26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T26" t="b">
-        <v>0</v>
-      </c>
-      <c r="U26" t="b">
-        <v>0</v>
-      </c>
-      <c r="V26" t="b">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y26" t="str">
+      <c r="P32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Resistors - </v>
       </c>
-      <c r="Z26" t="str">
+      <c r="Z32" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Network</v>
       </c>
-      <c r="AA26" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB26" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC26" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD26" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE26" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="3:31">
-      <c r="H27" t="str">
+      <c r="AA32" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB32" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC32" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD32" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE32" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H33" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - PCB Mount - DC-DC - Isolated</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I33" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J33" t="s">
         <v>69</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K33" t="s">
         <v>83</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L33" t="s">
         <v>84</v>
       </c>
-      <c r="P27" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27" t="b">
-        <v>1</v>
-      </c>
-      <c r="S27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T27" t="b">
-        <v>1</v>
-      </c>
-      <c r="U27" t="b">
-        <v>1</v>
-      </c>
-      <c r="V27" t="s">
+      <c r="P33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+      <c r="U33" t="b">
+        <v>1</v>
+      </c>
+      <c r="V33" t="s">
         <v>184</v>
       </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27" s="6">
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>85.714285714285708</v>
       </c>
-      <c r="Y27" t="str">
+      <c r="Y33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">PSUs - </v>
       </c>
-      <c r="Z27" t="str">
+      <c r="Z33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">PCB Mount - </v>
       </c>
-      <c r="AA27" t="str">
+      <c r="AA33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v xml:space="preserve">DC-DC - </v>
       </c>
-      <c r="AB27" t="str">
+      <c r="AB33" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
         <v>Isolated</v>
       </c>
-      <c r="AC27" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD27" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE27" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="3:31">
-      <c r="H28" t="str">
+      <c r="AC33" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD33" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE33" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H34" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - PCB Mount - AC-DC</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I34" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J34" t="s">
         <v>69</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K34" t="s">
         <v>82</v>
       </c>
-      <c r="P28" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="b">
-        <v>0</v>
-      </c>
-      <c r="R28" t="b">
-        <v>0</v>
-      </c>
-      <c r="S28" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T28" t="b">
-        <v>0</v>
-      </c>
-      <c r="U28" t="b">
-        <v>0</v>
-      </c>
-      <c r="V28" t="b">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28" s="6">
+      <c r="P34" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34" s="6">
         <v>5</v>
       </c>
-      <c r="Y28" t="str">
+      <c r="Y34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">PSUs - </v>
       </c>
-      <c r="Z28" t="str">
+      <c r="Z34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">PCB Mount - </v>
       </c>
-      <c r="AA28" t="str">
+      <c r="AA34" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>AC-DC</v>
       </c>
-      <c r="AB28" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC28" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD28" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE28" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="3:31">
-      <c r="H29" t="str">
+      <c r="AB34" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC34" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD34" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE34" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H35" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - Chasis Mount - DC-DC</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I35" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J35" t="s">
         <v>86</v>
       </c>
-      <c r="K29" t="s">
+      <c r="K35" t="s">
         <v>83</v>
       </c>
-      <c r="P29" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>0</v>
-      </c>
-      <c r="R29" t="b">
-        <v>0</v>
-      </c>
-      <c r="S29" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T29" t="b">
-        <v>0</v>
-      </c>
-      <c r="U29" t="b">
-        <v>0</v>
-      </c>
-      <c r="V29" t="b">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y29" t="str">
+      <c r="P35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">PSUs - </v>
       </c>
-      <c r="Z29" t="str">
+      <c r="Z35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Chasis Mount - </v>
       </c>
-      <c r="AA29" t="str">
+      <c r="AA35" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>DC-DC</v>
       </c>
-      <c r="AB29" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC29" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD29" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE29" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="3:31">
-      <c r="H30" t="str">
+      <c r="AB35" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC35" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD35" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE35" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H36" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - Chasis Mount - AC-DC</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I36" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J36" t="s">
         <v>86</v>
       </c>
-      <c r="K30" t="s">
+      <c r="K36" t="s">
         <v>82</v>
       </c>
-      <c r="P30" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" t="b">
-        <v>0</v>
-      </c>
-      <c r="U30" t="b">
-        <v>0</v>
-      </c>
-      <c r="V30" t="b">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y30" t="str">
+      <c r="P36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">PSUs - </v>
       </c>
-      <c r="Z30" t="str">
+      <c r="Z36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Chasis Mount - </v>
       </c>
-      <c r="AA30" t="str">
+      <c r="AA36" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>AC-DC</v>
       </c>
-      <c r="AB30" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC30" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD30" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE30" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="3:31">
-      <c r="H31" t="str">
+      <c r="AB36" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC36" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD36" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE36" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H37" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - PolyFuses</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J37" t="s">
         <v>180</v>
       </c>
-      <c r="P31" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="b">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T31" t="b">
-        <v>1</v>
-      </c>
-      <c r="U31" t="b">
-        <v>1</v>
-      </c>
-      <c r="V31" t="b">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31" s="6">
+      <c r="P37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="b">
+        <v>1</v>
+      </c>
+      <c r="U37" t="b">
+        <v>1</v>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>42.857142857142854</v>
       </c>
-      <c r="Y31" t="str">
+      <c r="Y37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Protection - </v>
       </c>
-      <c r="Z31" t="str">
+      <c r="Z37" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>PolyFuses</v>
       </c>
-      <c r="AA31" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB31" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC31" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD31" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE31" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="3:31">
-      <c r="H32" t="str">
+      <c r="AA37" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB37" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC37" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD37" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE37" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H38" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Standoffs  - SMD</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I38" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J38" t="s">
         <v>134</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K38" t="s">
         <v>44</v>
       </c>
-      <c r="P32" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="b">
-        <v>1</v>
-      </c>
-      <c r="R32" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T32" t="b">
-        <v>1</v>
-      </c>
-      <c r="U32" t="b">
-        <v>1</v>
-      </c>
-      <c r="V32" t="s">
+      <c r="P38" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="b">
+        <v>1</v>
+      </c>
+      <c r="U38" t="b">
+        <v>1</v>
+      </c>
+      <c r="V38" t="s">
         <v>184</v>
       </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32" s="6">
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>85.714285714285708</v>
       </c>
-      <c r="Y32" t="str">
+      <c r="Y38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Mechanical  - </v>
       </c>
-      <c r="Z32" t="str">
+      <c r="Z38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Standoffs  - </v>
       </c>
-      <c r="AA32" t="str">
+      <c r="AA38" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>SMD</v>
       </c>
-      <c r="AB32" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC32" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD32" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE32" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="8:31">
-      <c r="H33" t="str">
+      <c r="AB38" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC38" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD38" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE38" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H39" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Standoffs  - M_F</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I39" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J33" t="s">
+      <c r="J39" t="s">
         <v>134</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K39" t="s">
         <v>141</v>
       </c>
-      <c r="P33" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="b">
-        <v>0</v>
-      </c>
-      <c r="R33" t="b">
-        <v>0</v>
-      </c>
-      <c r="S33" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T33" t="b">
-        <v>0</v>
-      </c>
-      <c r="U33" t="b">
-        <v>0</v>
-      </c>
-      <c r="V33" t="b">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y33" t="str">
+      <c r="P39" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+      <c r="V39" t="b">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Mechanical  - </v>
       </c>
-      <c r="Z33" t="str">
+      <c r="Z39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Standoffs  - </v>
       </c>
-      <c r="AA33" t="str">
+      <c r="AA39" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>M_F</v>
       </c>
-      <c r="AB33" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC33" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD33" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE33" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="8:31">
-      <c r="H34" t="str">
+      <c r="AB39" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC39" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD39" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE39" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H40" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Standoffs  - F_F</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I40" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J40" t="s">
         <v>134</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K40" t="s">
         <v>142</v>
       </c>
-      <c r="P34" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T34" t="b">
-        <v>0</v>
-      </c>
-      <c r="U34" t="b">
-        <v>0</v>
-      </c>
-      <c r="V34" t="b">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y34" t="str">
+      <c r="P40" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="b">
+        <v>0</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Mechanical  - </v>
       </c>
-      <c r="Z34" t="str">
+      <c r="Z40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Standoffs  - </v>
       </c>
-      <c r="AA34" t="str">
+      <c r="AA40" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>F_F</v>
       </c>
-      <c r="AB34" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC34" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD34" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE34" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="8:31">
-      <c r="H35" t="str">
+      <c r="AB40" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC40" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD40" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE40" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H41" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Spacers</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I41" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J41" t="s">
         <v>135</v>
       </c>
-      <c r="P35" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" t="b">
-        <v>0</v>
-      </c>
-      <c r="S35" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T35" t="b">
-        <v>0</v>
-      </c>
-      <c r="U35" t="b">
-        <v>0</v>
-      </c>
-      <c r="V35" t="b">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y35" t="str">
+      <c r="P41" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="b">
+        <v>0</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+      <c r="V41" t="b">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Mechanical  - </v>
       </c>
-      <c r="Z35" t="str">
+      <c r="Z41" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Spacers</v>
       </c>
-      <c r="AA35" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB35" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC35" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD35" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE35" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="8:31">
-      <c r="H36" t="str">
+      <c r="AA41" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB41" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC41" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD41" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE41" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H42" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Nuts</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I42" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J42" t="s">
         <v>137</v>
       </c>
-      <c r="P36" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="b">
-        <v>0</v>
-      </c>
-      <c r="R36" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T36" t="b">
-        <v>0</v>
-      </c>
-      <c r="U36" t="b">
-        <v>0</v>
-      </c>
-      <c r="V36" t="b">
-        <v>0</v>
-      </c>
-      <c r="W36">
-        <v>0</v>
-      </c>
-      <c r="X36" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y36" t="str">
+      <c r="P42" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="b">
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Mechanical  - </v>
       </c>
-      <c r="Z36" t="str">
+      <c r="Z42" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Nuts</v>
       </c>
-      <c r="AA36" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB36" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC36" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD36" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE36" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="8:31">
-      <c r="H37" t="str">
+      <c r="AA42" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB42" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC42" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD42" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE42" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H43" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Heat Shrink</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I43" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J43" t="s">
         <v>147</v>
       </c>
-      <c r="P37" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" t="b">
-        <v>0</v>
-      </c>
-      <c r="S37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T37" t="b">
-        <v>0</v>
-      </c>
-      <c r="U37" t="b">
-        <v>0</v>
-      </c>
-      <c r="V37" t="b">
-        <v>0</v>
-      </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="X37" s="6">
+      <c r="P43" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="b">
+        <v>0</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>14.285714285714285</v>
       </c>
-      <c r="Y37" t="str">
+      <c r="Y43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Mechanical  - </v>
       </c>
-      <c r="Z37" t="str">
+      <c r="Z43" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Heat Shrink</v>
       </c>
-      <c r="AA37" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB37" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC37" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD37" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE37" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="8:31">
-      <c r="H38" t="str">
+      <c r="AA43" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB43" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC43" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD43" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE43" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H44" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>LEDs - RGB</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I44" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J44" t="s">
         <v>154</v>
       </c>
-      <c r="P38" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" t="b">
-        <v>0</v>
-      </c>
-      <c r="S38" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T38" t="b">
-        <v>1</v>
-      </c>
-      <c r="U38" t="b">
-        <v>1</v>
-      </c>
-      <c r="V38" t="b">
-        <v>0</v>
-      </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-      <c r="X38" s="6">
+      <c r="P44" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="b">
+        <v>1</v>
+      </c>
+      <c r="U44" t="b">
+        <v>1</v>
+      </c>
+      <c r="V44" t="b">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>28.571428571428569</v>
       </c>
-      <c r="Y38" t="str">
+      <c r="Y44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">LEDs - </v>
       </c>
-      <c r="Z38" t="str">
+      <c r="Z44" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>RGB</v>
       </c>
-      <c r="AA38" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB38" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC38" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD38" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE38" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="8:31">
-      <c r="H39" t="str">
+      <c r="AA44" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB44" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC44" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD44" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE44" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H45" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Isolators - Optoisolator</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I45" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J45" t="s">
         <v>217</v>
       </c>
-      <c r="P39" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="b">
-        <v>0</v>
-      </c>
-      <c r="R39" t="b">
-        <v>0</v>
-      </c>
-      <c r="S39" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="b">
-        <v>0</v>
-      </c>
-      <c r="U39" t="b">
-        <v>0</v>
-      </c>
-      <c r="V39" t="b">
-        <v>0</v>
-      </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
-      <c r="X39" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y39" t="str">
+      <c r="P45" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="b">
+        <v>0</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+      <c r="V45" t="b">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Isolators - </v>
       </c>
-      <c r="Z39" t="str">
+      <c r="Z45" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Optoisolator</v>
       </c>
-      <c r="AA39" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB39" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC39" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD39" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE39" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="8:31">
-      <c r="H40" t="str">
+      <c r="AA45" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB45" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC45" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD45" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE45" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H46" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Isolators - Digital</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I46" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J46" t="s">
         <v>98</v>
       </c>
-      <c r="P40" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="b">
-        <v>1</v>
-      </c>
-      <c r="R40" t="b">
-        <v>1</v>
-      </c>
-      <c r="S40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T40" t="b">
-        <v>1</v>
-      </c>
-      <c r="U40" t="b">
-        <v>1</v>
-      </c>
-      <c r="V40" t="s">
+      <c r="P46" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>1</v>
+      </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
+      <c r="S46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="b">
+        <v>1</v>
+      </c>
+      <c r="U46" t="b">
+        <v>1</v>
+      </c>
+      <c r="V46" t="s">
         <v>184</v>
       </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40" s="6">
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>85.714285714285708</v>
       </c>
-      <c r="Y40" t="str">
+      <c r="Y46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Isolators - </v>
       </c>
-      <c r="Z40" t="str">
+      <c r="Z46" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Digital</v>
       </c>
-      <c r="AA40" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB40" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC40" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD40" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE40" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="8:31">
-      <c r="H41" t="str">
+      <c r="AA46" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB46" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC46" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD46" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE46" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H47" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Isolators - Analog</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I47" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J47" t="s">
         <v>99</v>
       </c>
-      <c r="P41" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="b">
-        <v>0</v>
-      </c>
-      <c r="R41" t="b">
-        <v>0</v>
-      </c>
-      <c r="S41" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T41" t="b">
-        <v>0</v>
-      </c>
-      <c r="U41" t="b">
-        <v>1</v>
-      </c>
-      <c r="V41" t="b">
-        <v>0</v>
-      </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
-      <c r="X41" s="6">
+      <c r="P47" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47" t="b">
+        <v>0</v>
+      </c>
+      <c r="S47" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U47" t="b">
+        <v>1</v>
+      </c>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>14.285714285714285</v>
       </c>
-      <c r="Y41" t="str">
+      <c r="Y47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Isolators - </v>
       </c>
-      <c r="Z41" t="str">
+      <c r="Z47" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Analog</v>
       </c>
-      <c r="AA41" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB41" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC41" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD41" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE41" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="8:31">
-      <c r="H42" t="str">
+      <c r="AA47" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB47" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC47" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD47" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE47" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H48" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Inductors - Common Mode Choke</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I48" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J48" t="s">
         <v>80</v>
       </c>
-      <c r="P42" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="b">
-        <v>1</v>
-      </c>
-      <c r="R42" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T42" t="b">
-        <v>1</v>
-      </c>
-      <c r="U42" t="b">
-        <v>1</v>
-      </c>
-      <c r="V42" t="s">
+      <c r="P48" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
+      <c r="S48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="b">
+        <v>1</v>
+      </c>
+      <c r="U48" t="b">
+        <v>1</v>
+      </c>
+      <c r="V48" t="s">
         <v>184</v>
       </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42" s="6">
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>85.714285714285708</v>
       </c>
-      <c r="Y42" t="str">
+      <c r="Y48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Inductors - </v>
       </c>
-      <c r="Z42" t="str">
+      <c r="Z48" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Common Mode Choke</v>
       </c>
-      <c r="AA42" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB42" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC42" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD42" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE42" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="8:31">
-      <c r="H43" t="str">
+      <c r="AA48" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB48" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC48" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD48" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE48" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H49" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - RTCs</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J43" t="s">
-        <v>209</v>
-      </c>
-      <c r="P43" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="b">
-        <v>1</v>
-      </c>
-      <c r="R43" t="b">
-        <v>1</v>
-      </c>
-      <c r="S43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T43" t="b">
-        <v>1</v>
-      </c>
-      <c r="U43" t="b">
-        <v>1</v>
-      </c>
-      <c r="V43" t="s">
-        <v>184</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
-      </c>
-      <c r="Y43" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
-      </c>
-      <c r="Z43" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>RTCs</v>
-      </c>
-      <c r="AA43" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB43" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC43" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD43" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE43" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="8:31">
-      <c r="H44" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Switching Regulator</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J44" t="s">
-        <v>88</v>
-      </c>
-      <c r="K44" t="s">
-        <v>216</v>
-      </c>
-      <c r="P44" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="b">
-        <v>0</v>
-      </c>
-      <c r="R44" t="b">
-        <v>0</v>
-      </c>
-      <c r="S44" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T44" t="b">
-        <v>0</v>
-      </c>
-      <c r="U44" t="b">
-        <v>1</v>
-      </c>
-      <c r="V44" t="b">
-        <v>0</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
-      </c>
-      <c r="Y44" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
-      </c>
-      <c r="Z44" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
-      </c>
-      <c r="AA44" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Switching Regulator</v>
-      </c>
-      <c r="AB44" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC44" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD44" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE44" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="8:31">
-      <c r="H45" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Switching Controler</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J45" t="s">
-        <v>88</v>
-      </c>
-      <c r="K45" t="s">
-        <v>104</v>
-      </c>
-      <c r="P45" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="b">
-        <v>0</v>
-      </c>
-      <c r="R45" t="b">
-        <v>0</v>
-      </c>
-      <c r="S45" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T45" t="b">
-        <v>0</v>
-      </c>
-      <c r="U45" t="b">
-        <v>1</v>
-      </c>
-      <c r="V45" t="b">
-        <v>0</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
-      </c>
-      <c r="Y45" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
-      </c>
-      <c r="Z45" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
-      </c>
-      <c r="AA45" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Switching Controler</v>
-      </c>
-      <c r="AB45" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC45" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD45" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE45" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="8:31">
-      <c r="H46" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Supply Sequencing</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J46" t="s">
-        <v>88</v>
-      </c>
-      <c r="K46" t="s">
-        <v>199</v>
-      </c>
-      <c r="P46" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="b">
-        <v>0</v>
-      </c>
-      <c r="R46" t="b">
-        <v>0</v>
-      </c>
-      <c r="S46" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T46" t="b">
-        <v>0</v>
-      </c>
-      <c r="U46" t="b">
-        <v>0</v>
-      </c>
-      <c r="V46" t="b">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y46" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
-      </c>
-      <c r="Z46" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
-      </c>
-      <c r="AA46" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Supply Sequencing</v>
-      </c>
-      <c r="AB46" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC46" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD46" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE46" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="8:31">
-      <c r="H47" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Half&amp;H Bridge</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J47" t="s">
-        <v>88</v>
-      </c>
-      <c r="K47" t="s">
-        <v>139</v>
-      </c>
-      <c r="P47" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="b">
-        <v>0</v>
-      </c>
-      <c r="R47" t="b">
-        <v>0</v>
-      </c>
-      <c r="S47" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T47" t="b">
-        <v>0</v>
-      </c>
-      <c r="U47" t="b">
-        <v>1</v>
-      </c>
-      <c r="V47" t="b">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
-      </c>
-      <c r="Y47" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
-      </c>
-      <c r="Z47" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
-      </c>
-      <c r="AA47" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Half&amp;H Bridge</v>
-      </c>
-      <c r="AB47" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC47" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD47" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE47" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="8:31">
-      <c r="H48" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Gate Driver - Non Isolated</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J48" t="s">
-        <v>88</v>
-      </c>
-      <c r="K48" t="s">
-        <v>101</v>
-      </c>
-      <c r="L48" t="s">
-        <v>102</v>
-      </c>
-      <c r="P48" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="b">
-        <v>0</v>
-      </c>
-      <c r="R48" t="b">
-        <v>0</v>
-      </c>
-      <c r="S48" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T48" t="b">
-        <v>0</v>
-      </c>
-      <c r="U48" t="b">
-        <v>1</v>
-      </c>
-      <c r="V48" t="b">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
-      </c>
-      <c r="Y48" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">ICs - </v>
-      </c>
-      <c r="Z48" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
-      </c>
-      <c r="AA48" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Gate Driver - </v>
-      </c>
-      <c r="AB48" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Non Isolated</v>
-      </c>
-      <c r="AC48" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD48" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE48" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="8:31">
-      <c r="H49" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Power - Gate Driver - Isolated</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J49" t="s">
-        <v>88</v>
-      </c>
-      <c r="K49" t="s">
-        <v>101</v>
-      </c>
-      <c r="L49" t="s">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="P49" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="b">
         <v>1</v>
       </c>
-      <c r="V49" t="b">
-        <v>0</v>
+      <c r="V49" t="s">
+        <v>184</v>
       </c>
       <c r="W49">
         <v>0</v>
       </c>
       <c r="X49" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4367,15 +4356,15 @@
       </c>
       <c r="Z49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Power - </v>
+        <v>RTCs</v>
       </c>
       <c r="AA49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Gate Driver - </v>
+        <v/>
       </c>
       <c r="AB49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Isolated</v>
+        <v/>
       </c>
       <c r="AC49" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4390,19 +4379,19 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="8:31">
+    <row r="50" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H50" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - SD Card</v>
+        <v>ICs - Power - Switching Regulator</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J50" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="P50" s="6" t="b">
         <v>0</v>
@@ -4438,11 +4427,11 @@
       </c>
       <c r="Z50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SD Card</v>
+        <v>Switching Regulator</v>
       </c>
       <c r="AB50" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4461,47 +4450,47 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="8:31">
+    <row r="51" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H51" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - FLASH</v>
+        <v>ICs - Power - Switching Controler</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J51" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s">
-        <v>204</v>
+        <v>104</v>
       </c>
       <c r="P51" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="b">
         <v>1</v>
       </c>
-      <c r="V51" t="s">
-        <v>184</v>
+      <c r="V51" t="b">
+        <v>0</v>
       </c>
       <c r="W51">
         <v>0</v>
       </c>
       <c r="X51" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4509,11 +4498,11 @@
       </c>
       <c r="Z51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>FLASH</v>
+        <v>Switching Controler</v>
       </c>
       <c r="AB51" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4532,47 +4521,47 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="8:31">
+    <row r="52" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H52" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - EEPROM</v>
+        <v>ICs - Power - Supply Sequencing</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J52" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="P52" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="b">
-        <v>1</v>
-      </c>
-      <c r="V52" t="s">
-        <v>184</v>
+        <v>0</v>
+      </c>
+      <c r="V52" t="b">
+        <v>0</v>
       </c>
       <c r="W52">
         <v>0</v>
       </c>
       <c r="X52" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4580,11 +4569,11 @@
       </c>
       <c r="Z52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>EEPROM</v>
+        <v>Supply Sequencing</v>
       </c>
       <c r="AB52" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4603,19 +4592,19 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="8:31">
+    <row r="53" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H53" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Memory - DRAM</v>
+        <v>ICs - Power - Half&amp;H Bridge</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J53" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="P53" s="6" t="b">
         <v>0</v>
@@ -4651,11 +4640,11 @@
       </c>
       <c r="Z53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Memory - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DRAM</v>
+        <v>Half&amp;H Bridge</v>
       </c>
       <c r="AB53" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -4674,19 +4663,22 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="8:31">
+    <row r="54" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H54" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Translators</v>
+        <v>ICs - Power - Gate Driver - Non Isolated</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J54" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s">
-        <v>176</v>
+        <v>101</v>
+      </c>
+      <c r="L54" t="s">
+        <v>102</v>
       </c>
       <c r="P54" s="6" t="b">
         <v>0</v>
@@ -4722,15 +4714,15 @@
       </c>
       <c r="Z54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Translators</v>
+        <v xml:space="preserve">Gate Driver - </v>
       </c>
       <c r="AB54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Non Isolated</v>
       </c>
       <c r="AC54" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4745,22 +4737,22 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="8:31">
+    <row r="55" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H55" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Switch - Digital</v>
+        <v>ICs - Power - Gate Driver - Isolated</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J55" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="L55" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="P55" s="6" t="b">
         <v>0</v>
@@ -4796,15 +4788,15 @@
       </c>
       <c r="Z55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Power - </v>
       </c>
       <c r="AA55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Switch - </v>
+        <v xml:space="preserve">Gate Driver - </v>
       </c>
       <c r="AB55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v>Isolated</v>
       </c>
       <c r="AC55" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4819,50 +4811,47 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="8:31">
+    <row r="56" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H56" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Shift Registers - SIPO</v>
+        <v>ICs - Memory - FLASH</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J56" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="K56" t="s">
-        <v>170</v>
-      </c>
-      <c r="L56" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" t="b">
         <v>1</v>
       </c>
-      <c r="V56" t="b">
-        <v>0</v>
+      <c r="V56" t="s">
+        <v>184</v>
       </c>
       <c r="W56">
         <v>0</v>
       </c>
       <c r="X56" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4870,15 +4859,15 @@
       </c>
       <c r="Z56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Shift Registers - </v>
+        <v>FLASH</v>
       </c>
       <c r="AB56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SIPO</v>
+        <v/>
       </c>
       <c r="AC56" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4893,50 +4882,47 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="8:31">
+    <row r="57" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H57" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Shift Registers - PISO</v>
+        <v>ICs - Memory - EEPROM</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J57" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="K57" t="s">
-        <v>170</v>
-      </c>
-      <c r="L57" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="P57" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" t="b">
         <v>1</v>
       </c>
-      <c r="V57" t="b">
-        <v>0</v>
+      <c r="V57" t="s">
+        <v>184</v>
       </c>
       <c r="W57">
         <v>0</v>
       </c>
       <c r="X57" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -4944,15 +4930,15 @@
       </c>
       <c r="Z57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Shift Registers - </v>
+        <v>EEPROM</v>
       </c>
       <c r="AB57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>PISO</v>
+        <v/>
       </c>
       <c r="AC57" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -4967,19 +4953,19 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="8:31">
+    <row r="58" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H58" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Multivibrators</v>
+        <v>ICs - Memory - DRAM</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J58" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="K58" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="P58" s="6" t="b">
         <v>0</v>
@@ -5015,11 +5001,11 @@
       </c>
       <c r="Z58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Logic - </v>
+        <v xml:space="preserve">Memory - </v>
       </c>
       <c r="AA58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Multivibrators</v>
+        <v>DRAM</v>
       </c>
       <c r="AB58" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5038,10 +5024,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="8:31">
+    <row r="59" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H59" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Multiplexer - Digital</v>
+        <v>ICs - Logic - Translators</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>100</v>
@@ -5050,10 +5036,7 @@
         <v>118</v>
       </c>
       <c r="K59" t="s">
-        <v>174</v>
-      </c>
-      <c r="L59" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="P59" s="6" t="b">
         <v>0</v>
@@ -5093,11 +5076,11 @@
       </c>
       <c r="AA59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Multiplexer - </v>
+        <v>Translators</v>
       </c>
       <c r="AB59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC59" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5112,10 +5095,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="8:31">
+    <row r="60" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H60" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Level Shifters</v>
+        <v>ICs - Logic - Switch - Digital</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>100</v>
@@ -5124,7 +5107,10 @@
         <v>118</v>
       </c>
       <c r="K60" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="L60" t="s">
+        <v>98</v>
       </c>
       <c r="P60" s="6" t="b">
         <v>0</v>
@@ -5136,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="b">
         <v>0</v>
@@ -5152,7 +5138,7 @@
       </c>
       <c r="X60" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -5164,11 +5150,11 @@
       </c>
       <c r="AA60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Level Shifters</v>
+        <v xml:space="preserve">Switch - </v>
       </c>
       <c r="AB60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC60" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5183,10 +5169,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="8:31">
+    <row r="61" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H61" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Latches</v>
+        <v>ICs - Logic - Shift Registers - SIPO</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>100</v>
@@ -5195,7 +5181,10 @@
         <v>118</v>
       </c>
       <c r="K61" t="s">
-        <v>168</v>
+        <v>170</v>
+      </c>
+      <c r="L61" t="s">
+        <v>171</v>
       </c>
       <c r="P61" s="6" t="b">
         <v>0</v>
@@ -5235,11 +5224,11 @@
       </c>
       <c r="AA61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Latches</v>
+        <v xml:space="preserve">Shift Registers - </v>
       </c>
       <c r="AB61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>SIPO</v>
       </c>
       <c r="AC61" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5254,10 +5243,10 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="8:31">
+    <row r="62" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H62" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Gates</v>
+        <v>ICs - Logic - Shift Registers - PISO</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>100</v>
@@ -5266,7 +5255,10 @@
         <v>118</v>
       </c>
       <c r="K62" t="s">
-        <v>167</v>
+        <v>170</v>
+      </c>
+      <c r="L62" t="s">
+        <v>172</v>
       </c>
       <c r="P62" s="6" t="b">
         <v>0</v>
@@ -5306,11 +5298,11 @@
       </c>
       <c r="AA62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Gates</v>
+        <v xml:space="preserve">Shift Registers - </v>
       </c>
       <c r="AB62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>PISO</v>
       </c>
       <c r="AC62" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5325,10 +5317,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="8:31">
+    <row r="63" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H63" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Flip Flops</v>
+        <v>ICs - Logic - Multivibrators</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>100</v>
@@ -5337,7 +5329,7 @@
         <v>118</v>
       </c>
       <c r="K63" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="P63" s="6" t="b">
         <v>0</v>
@@ -5377,7 +5369,7 @@
       </c>
       <c r="AA63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Flip Flops</v>
+        <v>Multivibrators</v>
       </c>
       <c r="AB63" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5396,10 +5388,10 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="8:31">
+    <row r="64" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H64" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Demultiplexer - Digital</v>
+        <v>ICs - Logic - Multiplexer - Digital</v>
       </c>
       <c r="I64" s="6" t="s">
         <v>100</v>
@@ -5408,7 +5400,7 @@
         <v>118</v>
       </c>
       <c r="K64" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L64" t="s">
         <v>98</v>
@@ -5451,7 +5443,7 @@
       </c>
       <c r="AA64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Demultiplexer - </v>
+        <v xml:space="preserve">Multiplexer - </v>
       </c>
       <c r="AB64" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5470,10 +5462,10 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:31">
+    <row r="65" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H65" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Counter - Up&amp;Down</v>
+        <v>ICs - Logic - Level Shifters</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>100</v>
@@ -5482,10 +5474,7 @@
         <v>118</v>
       </c>
       <c r="K65" t="s">
-        <v>163</v>
-      </c>
-      <c r="L65" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="P65" s="6" t="b">
         <v>0</v>
@@ -5497,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="b">
         <v>0</v>
@@ -5513,7 +5502,7 @@
       </c>
       <c r="X65" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>28.571428571428569</v>
       </c>
       <c r="Y65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -5525,11 +5514,11 @@
       </c>
       <c r="AA65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Counter - </v>
+        <v>Level Shifters</v>
       </c>
       <c r="AB65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Up&amp;Down</v>
+        <v/>
       </c>
       <c r="AC65" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5544,10 +5533,10 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:31">
+    <row r="66" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H66" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Counter - Up</v>
+        <v>ICs - Logic - Latches</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>100</v>
@@ -5556,10 +5545,7 @@
         <v>118</v>
       </c>
       <c r="K66" t="s">
-        <v>163</v>
-      </c>
-      <c r="L66" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P66" s="6" t="b">
         <v>0</v>
@@ -5599,11 +5585,11 @@
       </c>
       <c r="AA66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Counter - </v>
+        <v>Latches</v>
       </c>
       <c r="AB66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Up</v>
+        <v/>
       </c>
       <c r="AC66" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5618,10 +5604,10 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:31">
+    <row r="67" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H67" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Logic - Comparator - Digital</v>
+        <v>ICs - Logic - Gates</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>100</v>
@@ -5630,10 +5616,7 @@
         <v>118</v>
       </c>
       <c r="K67" t="s">
-        <v>116</v>
-      </c>
-      <c r="L67" t="s">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="P67" s="6" t="b">
         <v>0</v>
@@ -5673,11 +5656,11 @@
       </c>
       <c r="AA67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">Comparator - </v>
+        <v>Gates</v>
       </c>
       <c r="AB67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>Digital</v>
+        <v/>
       </c>
       <c r="AC67" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5692,19 +5675,19 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:31">
+    <row r="68" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H68" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - UART</v>
+        <v>ICs - Logic - Flip Flops</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K68" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="P68" s="6" t="b">
         <v>0</v>
@@ -5740,11 +5723,11 @@
       </c>
       <c r="Z68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>UART</v>
+        <v>Flip Flops</v>
       </c>
       <c r="AB68" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -5763,19 +5746,22 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:31">
+    <row r="69" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H69" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Trancievers</v>
+        <v>ICs - Logic - Demultiplexer - Digital</v>
       </c>
       <c r="I69" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J69" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K69" t="s">
-        <v>122</v>
+        <v>175</v>
+      </c>
+      <c r="L69" t="s">
+        <v>98</v>
       </c>
       <c r="P69" s="6" t="b">
         <v>0</v>
@@ -5811,15 +5797,15 @@
       </c>
       <c r="Z69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Trancievers</v>
+        <v xml:space="preserve">Demultiplexer - </v>
       </c>
       <c r="AB69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC69" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5834,19 +5820,22 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:31">
+    <row r="70" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H70" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Serializer</v>
+        <v>ICs - Logic - Counter - Up&amp;Down</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J70" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K70" t="s">
-        <v>159</v>
+        <v>163</v>
+      </c>
+      <c r="L70" t="s">
+        <v>165</v>
       </c>
       <c r="P70" s="6" t="b">
         <v>0</v>
@@ -5882,15 +5871,15 @@
       </c>
       <c r="Z70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Serializer</v>
+        <v xml:space="preserve">Counter - </v>
       </c>
       <c r="AB70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Up&amp;Down</v>
       </c>
       <c r="AC70" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5905,19 +5894,22 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:31">
+    <row r="71" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H71" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Recievers</v>
+        <v>ICs - Logic - Counter - Up</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J71" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K71" t="s">
-        <v>121</v>
+        <v>163</v>
+      </c>
+      <c r="L71" t="s">
+        <v>164</v>
       </c>
       <c r="P71" s="6" t="b">
         <v>0</v>
@@ -5953,15 +5945,15 @@
       </c>
       <c r="Z71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Recievers</v>
+        <v xml:space="preserve">Counter - </v>
       </c>
       <c r="AB71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Up</v>
       </c>
       <c r="AC71" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -5976,19 +5968,22 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:31">
+    <row r="72" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H72" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - IO Expander</v>
+        <v>ICs - Logic - Comparator - Digital</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K72" t="s">
-        <v>155</v>
+        <v>116</v>
+      </c>
+      <c r="L72" t="s">
+        <v>98</v>
       </c>
       <c r="P72" s="6" t="b">
         <v>0</v>
@@ -6024,15 +6019,15 @@
       </c>
       <c r="Z72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Interface  - </v>
+        <v xml:space="preserve">Logic - </v>
       </c>
       <c r="AA72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>IO Expander</v>
+        <v xml:space="preserve">Comparator - </v>
       </c>
       <c r="AB72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
+        <v>Digital</v>
       </c>
       <c r="AC72" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6047,10 +6042,10 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:31">
+    <row r="73" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H73" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Drivers</v>
+        <v>ICs - Interface  - UART</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>100</v>
@@ -6059,7 +6054,7 @@
         <v>119</v>
       </c>
       <c r="K73" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="P73" s="6" t="b">
         <v>0</v>
@@ -6099,7 +6094,7 @@
       </c>
       <c r="AA73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Drivers</v>
+        <v>UART</v>
       </c>
       <c r="AB73" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6118,10 +6113,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:31">
+    <row r="74" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H74" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Deserializer</v>
+        <v>ICs - Interface  - Trancievers</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>100</v>
@@ -6130,7 +6125,7 @@
         <v>119</v>
       </c>
       <c r="K74" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="P74" s="6" t="b">
         <v>0</v>
@@ -6170,7 +6165,7 @@
       </c>
       <c r="AA74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Deserializer</v>
+        <v>Trancievers</v>
       </c>
       <c r="AB74" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6189,10 +6184,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:31">
+    <row r="75" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H75" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Controller</v>
+        <v>ICs - Interface  - Serializer</v>
       </c>
       <c r="I75" s="6" t="s">
         <v>100</v>
@@ -6201,7 +6196,7 @@
         <v>119</v>
       </c>
       <c r="K75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P75" s="6" t="b">
         <v>0</v>
@@ -6241,7 +6236,7 @@
       </c>
       <c r="AA75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Controller</v>
+        <v>Serializer</v>
       </c>
       <c r="AB75" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6260,10 +6255,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:31">
+    <row r="76" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H76" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Interface  - Analog Switch</v>
+        <v>ICs - Interface  - Recievers</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>100</v>
@@ -6272,7 +6267,7 @@
         <v>119</v>
       </c>
       <c r="K76" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="P76" s="6" t="b">
         <v>0</v>
@@ -6312,7 +6307,7 @@
       </c>
       <c r="AA76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Analog Switch</v>
+        <v>Recievers</v>
       </c>
       <c r="AB76" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6331,22 +6326,19 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:31">
+    <row r="77" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H77" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - PolarFire - SOC</v>
+        <v>ICs - Interface  - IO Expander</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J77" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="K77" t="s">
-        <v>109</v>
-      </c>
-      <c r="L77" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="P77" s="6" t="b">
         <v>0</v>
@@ -6382,15 +6374,15 @@
       </c>
       <c r="Z77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">PolarFire - </v>
+        <v>IO Expander</v>
       </c>
       <c r="AB77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>SOC</v>
+        <v/>
       </c>
       <c r="AC77" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -6405,22 +6397,22 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:31">
+    <row r="78" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H78" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Embedded - FPGA</v>
+        <v>ICs - Interface  - Drivers</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J78" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="K78" t="s">
-        <v>108</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>184</v>
+        <v>120</v>
+      </c>
+      <c r="P78" s="6" t="b">
+        <v>0</v>
       </c>
       <c r="Q78" t="b">
         <v>0</v>
@@ -6429,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T78" t="b">
         <v>0</v>
@@ -6445,7 +6437,7 @@
       </c>
       <c r="X78" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>28.571428571428569</v>
+        <v>14.285714285714285</v>
       </c>
       <c r="Y78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -6453,11 +6445,11 @@
       </c>
       <c r="Z78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Embedded - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>FPGA</v>
+        <v>Drivers</v>
       </c>
       <c r="AB78" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6476,19 +6468,19 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:31">
+    <row r="79" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H79" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - DAC</v>
+        <v>ICs - Interface  - Deserializer</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J79" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="K79" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="P79" s="6" t="b">
         <v>0</v>
@@ -6524,11 +6516,11 @@
       </c>
       <c r="Z79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>DAC</v>
+        <v>Deserializer</v>
       </c>
       <c r="AB79" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6547,19 +6539,19 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:31">
+    <row r="80" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H80" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - Comparator</v>
+        <v>ICs - Interface  - Controller</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J80" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="K80" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="P80" s="6" t="b">
         <v>0</v>
@@ -6595,11 +6587,11 @@
       </c>
       <c r="Z80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Analog - </v>
+        <v xml:space="preserve">Interface  - </v>
       </c>
       <c r="AA80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Comparator</v>
+        <v>Controller</v>
       </c>
       <c r="AB80" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6618,294 +6610,297 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:31">
+    <row r="81" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H81" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>ICs - Analog - ADC</v>
+        <v>ICs - Embedded - PolarFire - SOC</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J81" t="s">
+        <v>106</v>
+      </c>
+      <c r="K81" t="s">
+        <v>109</v>
+      </c>
+      <c r="L81" t="s">
+        <v>183</v>
+      </c>
+      <c r="P81" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="b">
+        <v>0</v>
+      </c>
+      <c r="R81" t="b">
+        <v>0</v>
+      </c>
+      <c r="S81" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T81" t="b">
+        <v>0</v>
+      </c>
+      <c r="U81" t="b">
+        <v>1</v>
+      </c>
+      <c r="V81" t="b">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="Y81" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">ICs - </v>
+      </c>
+      <c r="Z81" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Embedded - </v>
+      </c>
+      <c r="AA81" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v xml:space="preserve">PolarFire - </v>
+      </c>
+      <c r="AB81" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v>SOC</v>
+      </c>
+      <c r="AC81" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD81" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE81" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H82" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>ICs - Embedded - FPGA</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J82" t="s">
+        <v>106</v>
+      </c>
+      <c r="K82" t="s">
+        <v>108</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q82" t="b">
+        <v>0</v>
+      </c>
+      <c r="R82" t="b">
+        <v>0</v>
+      </c>
+      <c r="S82" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="b">
+        <v>0</v>
+      </c>
+      <c r="U82" t="b">
+        <v>1</v>
+      </c>
+      <c r="V82" t="b">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>28.571428571428569</v>
+      </c>
+      <c r="Y82" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">ICs - </v>
+      </c>
+      <c r="Z82" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Embedded - </v>
+      </c>
+      <c r="AA82" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>FPGA</v>
+      </c>
+      <c r="AB82" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC82" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD82" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE82" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H83" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>ICs - Analog - DAC</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J83" t="s">
         <v>99</v>
       </c>
-      <c r="K81" t="s">
-        <v>114</v>
-      </c>
-      <c r="P81" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q81" t="b">
-        <v>1</v>
-      </c>
-      <c r="R81" t="b">
-        <v>1</v>
-      </c>
-      <c r="S81" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T81" t="b">
-        <v>1</v>
-      </c>
-      <c r="U81" t="b">
-        <v>1</v>
-      </c>
-      <c r="V81" t="s">
-        <v>184</v>
-      </c>
-      <c r="W81">
-        <v>0</v>
-      </c>
-      <c r="X81" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
-      </c>
-      <c r="Y81" t="str">
+      <c r="K83" t="s">
+        <v>115</v>
+      </c>
+      <c r="P83" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="b">
+        <v>0</v>
+      </c>
+      <c r="R83" t="b">
+        <v>0</v>
+      </c>
+      <c r="S83" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="b">
+        <v>0</v>
+      </c>
+      <c r="U83" t="b">
+        <v>1</v>
+      </c>
+      <c r="V83" t="b">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="X83" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="Y83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">ICs - </v>
       </c>
-      <c r="Z81" t="str">
+      <c r="Z83" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Analog - </v>
       </c>
-      <c r="AA81" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>ADC</v>
-      </c>
-      <c r="AB81" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC81" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD81" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE81" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="8:31">
-      <c r="H82" t="str">
+      <c r="AA83" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>DAC</v>
+      </c>
+      <c r="AB83" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC83" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD83" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE83" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H84" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>ICs - Analog - Comparator</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J84" t="s">
+        <v>99</v>
+      </c>
+      <c r="K84" t="s">
+        <v>116</v>
+      </c>
+      <c r="P84" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="b">
+        <v>0</v>
+      </c>
+      <c r="R84" t="b">
+        <v>0</v>
+      </c>
+      <c r="S84" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T84" t="b">
+        <v>0</v>
+      </c>
+      <c r="U84" t="b">
+        <v>1</v>
+      </c>
+      <c r="V84" t="b">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="Y84" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">ICs - </v>
+      </c>
+      <c r="Z84" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Analog - </v>
+      </c>
+      <c r="AA84" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>Comparator</v>
+      </c>
+      <c r="AB84" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC84" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD84" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE84" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H85" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Transistors - SiCFET</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J82" t="s">
-        <v>194</v>
-      </c>
-      <c r="K82" t="s">
-        <v>95</v>
-      </c>
-      <c r="P82" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="b">
-        <v>0</v>
-      </c>
-      <c r="R82" t="b">
-        <v>0</v>
-      </c>
-      <c r="S82" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T82" t="b">
-        <v>1</v>
-      </c>
-      <c r="U82" t="b">
-        <v>0</v>
-      </c>
-      <c r="V82" t="b">
-        <v>0</v>
-      </c>
-      <c r="W82">
-        <v>0</v>
-      </c>
-      <c r="X82" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
-      </c>
-      <c r="Y82" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
-      </c>
-      <c r="Z82" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
-      </c>
-      <c r="AA82" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>SiCFET</v>
-      </c>
-      <c r="AB82" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC82" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD82" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE82" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="8:31">
-      <c r="H83" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - MOSFET</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J83" t="s">
-        <v>194</v>
-      </c>
-      <c r="K83" t="s">
-        <v>93</v>
-      </c>
-      <c r="P83" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q83" t="b">
-        <v>1</v>
-      </c>
-      <c r="R83" t="b">
-        <v>1</v>
-      </c>
-      <c r="S83" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T83" t="b">
-        <v>1</v>
-      </c>
-      <c r="U83" t="b">
-        <v>1</v>
-      </c>
-      <c r="V83" t="b">
-        <v>0</v>
-      </c>
-      <c r="W83">
-        <v>0</v>
-      </c>
-      <c r="X83" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
-      </c>
-      <c r="Y83" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
-      </c>
-      <c r="Z83" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
-      </c>
-      <c r="AA83" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>MOSFET</v>
-      </c>
-      <c r="AB83" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC83" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD83" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE83" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="8:31">
-      <c r="H84" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - JFET</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J84" t="s">
-        <v>194</v>
-      </c>
-      <c r="K84" t="s">
-        <v>96</v>
-      </c>
-      <c r="P84" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="b">
-        <v>0</v>
-      </c>
-      <c r="R84" t="b">
-        <v>0</v>
-      </c>
-      <c r="S84" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U84" t="b">
-        <v>0</v>
-      </c>
-      <c r="V84" t="b">
-        <v>0</v>
-      </c>
-      <c r="W84">
-        <v>0</v>
-      </c>
-      <c r="X84" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
-      </c>
-      <c r="Y84" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Discreet - </v>
-      </c>
-      <c r="Z84" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Transistors - </v>
-      </c>
-      <c r="AA84" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>JFET</v>
-      </c>
-      <c r="AB84" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC84" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD84" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE84" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="8:31">
-      <c r="H85" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - GaNFET</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>89</v>
@@ -6914,7 +6909,7 @@
         <v>194</v>
       </c>
       <c r="K85" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P85" s="6" t="b">
         <v>0</v>
@@ -6954,7 +6949,7 @@
       </c>
       <c r="AA85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>GaNFET</v>
+        <v>SiCFET</v>
       </c>
       <c r="AB85" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
@@ -6973,10 +6968,10 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:31">
+    <row r="86" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H86" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Transistors - BJT - PNP</v>
+        <v>Discreet - Transistors - MOSFET</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>89</v>
@@ -6985,25 +6980,22 @@
         <v>194</v>
       </c>
       <c r="K86" t="s">
-        <v>92</v>
-      </c>
-      <c r="L86" t="s">
-        <v>201</v>
+        <v>93</v>
       </c>
       <c r="P86" s="6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U86" t="b">
         <v>1</v>
@@ -7016,7 +7008,7 @@
       </c>
       <c r="X86" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>14.285714285714285</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="Y86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
@@ -7028,11 +7020,11 @@
       </c>
       <c r="AA86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v xml:space="preserve">BJT - </v>
+        <v>MOSFET</v>
       </c>
       <c r="AB86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v>PNP</v>
+        <v/>
       </c>
       <c r="AC86" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
@@ -7047,467 +7039,476 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:31">
+    <row r="87" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H87" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Discreet - Diodes - Standard</v>
+        <v>Discreet - Transistors - JFET</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J87" t="s">
+        <v>194</v>
+      </c>
+      <c r="K87" t="s">
+        <v>96</v>
+      </c>
+      <c r="P87" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="b">
+        <v>0</v>
+      </c>
+      <c r="R87" t="b">
+        <v>0</v>
+      </c>
+      <c r="S87" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T87" t="b">
+        <v>1</v>
+      </c>
+      <c r="U87" t="b">
+        <v>0</v>
+      </c>
+      <c r="V87" t="b">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+      <c r="X87" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="Y87" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Discreet - </v>
+      </c>
+      <c r="Z87" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Transistors - </v>
+      </c>
+      <c r="AA87" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>JFET</v>
+      </c>
+      <c r="AB87" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC87" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD87" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE87" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H88" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Discreet - Transistors - GaNFET</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J88" t="s">
+        <v>194</v>
+      </c>
+      <c r="K88" t="s">
+        <v>94</v>
+      </c>
+      <c r="P88" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="b">
+        <v>0</v>
+      </c>
+      <c r="R88" t="b">
+        <v>0</v>
+      </c>
+      <c r="S88" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T88" t="b">
+        <v>1</v>
+      </c>
+      <c r="U88" t="b">
+        <v>0</v>
+      </c>
+      <c r="V88" t="b">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="Y88" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Discreet - </v>
+      </c>
+      <c r="Z88" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Transistors - </v>
+      </c>
+      <c r="AA88" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v>GaNFET</v>
+      </c>
+      <c r="AB88" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC88" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD88" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE88" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H89" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Discreet - Transistors - BJT - PNP</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J89" t="s">
+        <v>194</v>
+      </c>
+      <c r="K89" t="s">
+        <v>92</v>
+      </c>
+      <c r="L89" t="s">
+        <v>201</v>
+      </c>
+      <c r="P89" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="b">
+        <v>0</v>
+      </c>
+      <c r="R89" t="b">
+        <v>0</v>
+      </c>
+      <c r="S89" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T89" t="b">
+        <v>0</v>
+      </c>
+      <c r="U89" t="b">
+        <v>1</v>
+      </c>
+      <c r="V89" t="b">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+      <c r="X89" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="Y89" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
+        <v xml:space="preserve">Discreet - </v>
+      </c>
+      <c r="Z89" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
+        <v xml:space="preserve">Transistors - </v>
+      </c>
+      <c r="AA89" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v xml:space="preserve">BJT - </v>
+      </c>
+      <c r="AB89" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v>PNP</v>
+      </c>
+      <c r="AC89" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD89" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE89" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H90" t="str">
+        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
+        <v>Discreet - Diodes - Standard</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J90" t="s">
         <v>90</v>
       </c>
-      <c r="K87" t="s">
+      <c r="K90" t="s">
         <v>63</v>
       </c>
-      <c r="P87" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="b">
-        <v>0</v>
-      </c>
-      <c r="R87" t="b">
-        <v>0</v>
-      </c>
-      <c r="S87" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T87" t="b">
-        <v>1</v>
-      </c>
-      <c r="U87" t="b">
-        <v>1</v>
-      </c>
-      <c r="V87" t="b">
-        <v>0</v>
-      </c>
-      <c r="W87">
-        <v>0</v>
-      </c>
-      <c r="X87" s="6">
+      <c r="P90" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="b">
+        <v>0</v>
+      </c>
+      <c r="R90" t="b">
+        <v>0</v>
+      </c>
+      <c r="S90" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T90" t="b">
+        <v>1</v>
+      </c>
+      <c r="U90" t="b">
+        <v>1</v>
+      </c>
+      <c r="V90" t="b">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90" s="6">
         <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
         <v>28.571428571428569</v>
       </c>
-      <c r="Y87" t="str">
+      <c r="Y90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Discreet - </v>
       </c>
-      <c r="Z87" t="str">
+      <c r="Z90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v xml:space="preserve">Diodes - </v>
       </c>
-      <c r="AA87" t="str">
+      <c r="AA90" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v>Standard</v>
       </c>
-      <c r="AB87" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC87" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD87" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE87" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="8:31">
-      <c r="H88" t="str">
+      <c r="AB90" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC90" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD90" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE90" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H91" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Contacts - Ring Terminals</v>
       </c>
-      <c r="I88" s="6" t="s">
+      <c r="I91" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J91" t="s">
         <v>77</v>
       </c>
-      <c r="P88" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="b">
-        <v>0</v>
-      </c>
-      <c r="R88" t="b">
-        <v>0</v>
-      </c>
-      <c r="S88" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T88" t="b">
-        <v>0</v>
-      </c>
-      <c r="U88" t="b">
-        <v>0</v>
-      </c>
-      <c r="V88" t="b">
-        <v>0</v>
-      </c>
-      <c r="W88">
-        <v>0</v>
-      </c>
-      <c r="X88" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y88" t="str">
+      <c r="P91" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="b">
+        <v>0</v>
+      </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
+      <c r="S91" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T91" t="b">
+        <v>0</v>
+      </c>
+      <c r="U91" t="b">
+        <v>0</v>
+      </c>
+      <c r="V91" t="b">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
+      </c>
+      <c r="X91" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Contacts - </v>
       </c>
-      <c r="Z88" t="str">
+      <c r="Z91" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Ring Terminals</v>
       </c>
-      <c r="AA88" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB88" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC88" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD88" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE88" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="8:31">
-      <c r="H89" t="str">
+      <c r="AA91" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB91" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC91" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD91" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE91" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H92" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Contacts - Ferrules</v>
       </c>
-      <c r="I89" s="6" t="s">
+      <c r="I92" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J92" t="s">
         <v>76</v>
       </c>
-      <c r="P89" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="b">
-        <v>0</v>
-      </c>
-      <c r="R89" t="b">
-        <v>0</v>
-      </c>
-      <c r="S89" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T89" t="b">
-        <v>0</v>
-      </c>
-      <c r="U89" t="b">
-        <v>0</v>
-      </c>
-      <c r="V89" t="b">
-        <v>0</v>
-      </c>
-      <c r="W89">
-        <v>0</v>
-      </c>
-      <c r="X89" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y89" t="str">
+      <c r="P92" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="b">
+        <v>0</v>
+      </c>
+      <c r="R92" t="b">
+        <v>0</v>
+      </c>
+      <c r="S92" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T92" t="b">
+        <v>0</v>
+      </c>
+      <c r="U92" t="b">
+        <v>0</v>
+      </c>
+      <c r="V92" t="b">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
+      </c>
+      <c r="X92" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Contacts - </v>
       </c>
-      <c r="Z89" t="str">
+      <c r="Z92" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Ferrules</v>
       </c>
-      <c r="AA89" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB89" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC89" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD89" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE89" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="8:31">
-      <c r="H90" t="str">
+      <c r="AA92" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
+        <v/>
+      </c>
+      <c r="AB92" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
+        <v/>
+      </c>
+      <c r="AC92" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
+        <v/>
+      </c>
+      <c r="AD92" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
+        <v/>
+      </c>
+      <c r="AE92" t="str">
+        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="8:31" x14ac:dyDescent="0.35">
+      <c r="H93" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Contacts - Banana Plugs</v>
       </c>
-      <c r="I90" s="6" t="s">
+      <c r="I93" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J93" t="s">
         <v>78</v>
       </c>
-      <c r="P90" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="b">
-        <v>0</v>
-      </c>
-      <c r="R90" t="b">
-        <v>0</v>
-      </c>
-      <c r="S90" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T90" t="b">
-        <v>0</v>
-      </c>
-      <c r="U90" t="b">
-        <v>0</v>
-      </c>
-      <c r="V90" t="b">
-        <v>0</v>
-      </c>
-      <c r="W90">
-        <v>0</v>
-      </c>
-      <c r="X90" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>0</v>
-      </c>
-      <c r="Y90" t="str">
+      <c r="P93" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="b">
+        <v>0</v>
+      </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
+      <c r="S93" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T93" t="b">
+        <v>0</v>
+      </c>
+      <c r="U93" t="b">
+        <v>0</v>
+      </c>
+      <c r="V93" t="b">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
+      </c>
+      <c r="X93" s="6">
+        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
+        <v>0</v>
+      </c>
+      <c r="Y93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
         <v xml:space="preserve">Contacts - </v>
       </c>
-      <c r="Z90" t="str">
+      <c r="Z93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
         <v>Banana Plugs</v>
       </c>
-      <c r="AA90" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB90" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC90" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD90" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE90" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="8:31">
-      <c r="H91" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Test Points</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J91" t="s">
-        <v>189</v>
-      </c>
-      <c r="P91" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="b">
-        <v>1</v>
-      </c>
-      <c r="R91" t="b">
-        <v>1</v>
-      </c>
-      <c r="S91" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T91" t="b">
-        <v>1</v>
-      </c>
-      <c r="U91" t="b">
-        <v>1</v>
-      </c>
-      <c r="V91" t="s">
-        <v>184</v>
-      </c>
-      <c r="W91">
-        <v>0</v>
-      </c>
-      <c r="X91" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
-      </c>
-      <c r="Y91" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
-      </c>
-      <c r="Z91" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>Test Points</v>
-      </c>
-      <c r="AA91" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v/>
-      </c>
-      <c r="AB91" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC91" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD91" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE91" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="8:31">
-      <c r="H92" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - Terminal Blocks - Wire to Board</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J92" t="s">
-        <v>61</v>
-      </c>
-      <c r="K92" t="s">
-        <v>215</v>
-      </c>
-      <c r="P92" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q92" t="b">
-        <v>1</v>
-      </c>
-      <c r="R92" t="b">
-        <v>1</v>
-      </c>
-      <c r="S92" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T92" t="b">
-        <v>1</v>
-      </c>
-      <c r="U92" t="b">
-        <v>1</v>
-      </c>
-      <c r="V92" t="s">
-        <v>184</v>
-      </c>
-      <c r="W92">
-        <v>0</v>
-      </c>
-      <c r="X92" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
-      </c>
-      <c r="Y92" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
-      </c>
-      <c r="Z92" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v xml:space="preserve">Terminal Blocks - </v>
-      </c>
-      <c r="AA92" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
-        <v>Wire to Board</v>
-      </c>
-      <c r="AB92" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 4]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,Table1[[#This Row],[Part 4]],""))</f>
-        <v/>
-      </c>
-      <c r="AC92" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 5]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 5]])=0,Table1[[#This Row],[Part 5]],""))</f>
-        <v/>
-      </c>
-      <c r="AD92" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 6]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 6]])=0,Table1[[#This Row],[Part 6]],""))</f>
-        <v/>
-      </c>
-      <c r="AE92" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 7]])=0,Table1[[#This Row],[Part 7]],"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="8:31">
-      <c r="H93" t="str">
-        <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
-        <v>Connectors - SD Card Socket</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J93" t="s">
-        <v>56</v>
-      </c>
-      <c r="P93" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q93" t="b">
-        <v>1</v>
-      </c>
-      <c r="R93" t="b">
-        <v>1</v>
-      </c>
-      <c r="S93" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T93" t="b">
-        <v>1</v>
-      </c>
-      <c r="U93" t="b">
-        <v>1</v>
-      </c>
-      <c r="V93" t="s">
-        <v>184</v>
-      </c>
-      <c r="W93">
-        <v>0</v>
-      </c>
-      <c r="X93" s="6">
-        <f>(COUNTIF(Table1[[#This Row],[Spreadsheet]:[Functionality Verified?]],"=TRUE")/7) * 100</f>
-        <v>85.714285714285708</v>
-      </c>
-      <c r="Y93" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 1]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 1]])=0,Table1[[#This Row],[Part 1]],""))</f>
-        <v xml:space="preserve">Connectors - </v>
-      </c>
-      <c r="Z93" t="str">
-        <f>IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 2]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 2]])=0,Table1[[#This Row],[Part 2]],""))</f>
-        <v>SD Card Socket</v>
-      </c>
       <c r="AA93" t="str">
         <f>IF(COUNTBLANK(Table1[[#This Row],[Part 4]])=0,_xlfn.CONCAT(Table1[[#This Row],[Part 3]]," - "),IF(COUNTBLANK(Table1[[#This Row],[Part 3]])=0,Table1[[#This Row],[Part 3]],""))</f>
         <v/>
@@ -7529,7 +7530,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:31">
+    <row r="94" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H94" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Screw Connectors</v>
@@ -7597,7 +7598,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:31">
+    <row r="95" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H95" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Power Entry Modules</v>
@@ -7665,7 +7666,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:31">
+    <row r="96" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H96" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Jumpers</v>
@@ -7733,7 +7734,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:31">
+    <row r="97" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H97" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Flat Flex</v>
@@ -7801,7 +7802,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:31">
+    <row r="98" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H98" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Standard - Male - PCB Mount</v>
@@ -7878,7 +7879,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:31">
+    <row r="99" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H99" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Standard - Male - Inline</v>
@@ -7955,7 +7956,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:31">
+    <row r="100" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H100" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Standard - Female - PCB Mount</v>
@@ -8032,7 +8033,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:31">
+    <row r="101" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H101" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Standard - Female - Inline</v>
@@ -8109,7 +8110,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:31">
+    <row r="102" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H102" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Hybrid - Male - Inline</v>
@@ -8186,7 +8187,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:31">
+    <row r="103" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H103" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Hybrid - Female - Inline</v>
@@ -8263,7 +8264,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:31">
+    <row r="104" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H104" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - D-Sub - Backshells</v>
@@ -8334,7 +8335,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:31">
+    <row r="105" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H105" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Coaxial</v>
@@ -8402,7 +8403,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:31">
+    <row r="106" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H106" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Card Edge</v>
@@ -8470,7 +8471,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:31">
+    <row r="107" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H107" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Battery Holders - Cylindrical</v>
@@ -8541,7 +8542,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:31">
+    <row r="108" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H108" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Battery Holders - Coin Cell</v>
@@ -8612,7 +8613,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:31">
+    <row r="109" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H109" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Banana Jacks</v>
@@ -8680,7 +8681,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:31">
+    <row r="110" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H110" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - VCOs - VCXO</v>
@@ -8754,7 +8755,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:31">
+    <row r="111" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H111" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - VCOs - VCTCXO</v>
@@ -8828,7 +8829,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:31">
+    <row r="112" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H112" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - VCOs - VCO</v>
@@ -8902,7 +8903,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:31">
+    <row r="113" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H113" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - Fixed - TCXO</v>
@@ -8976,7 +8977,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:31">
+    <row r="114" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H114" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - Fixed - Logic_Out</v>
@@ -9050,7 +9051,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:31">
+    <row r="115" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H115" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - Fixed - Ceramic Resonator</v>
@@ -9124,7 +9125,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:31">
+    <row r="116" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H116" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - ICs - DDS</v>
@@ -9195,7 +9196,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:31">
+    <row r="117" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H117" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Capacitors - Polarized</v>
@@ -9263,7 +9264,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:31">
+    <row r="118" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H118" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Voltage References - Burried Zener</v>
@@ -9331,7 +9332,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:31">
+    <row r="119" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H119" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Thermal - Pads</v>
@@ -9399,7 +9400,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:31">
+    <row r="120" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H120" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Thermal - Heat Sinks</v>
@@ -9467,7 +9468,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:31">
+    <row r="121" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H121" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Switches - Tactile</v>
@@ -9535,7 +9536,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:31">
+    <row r="122" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H122" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Switches - Slide</v>
@@ -9603,7 +9604,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:31">
+    <row r="123" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H123" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Switches - Push</v>
@@ -9671,7 +9672,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:31">
+    <row r="124" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H124" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Resistors - Single - SMD</v>
@@ -9742,7 +9743,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:31">
+    <row r="125" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H125" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Resistors - Isolated Array</v>
@@ -9810,7 +9811,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:31">
+    <row r="126" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H126" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - Wall Wart</v>
@@ -9878,7 +9879,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:31">
+    <row r="127" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H127" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>PSUs - PCB Mount - DC-DC - Non-Isolated</v>
@@ -9952,7 +9953,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:31">
+    <row r="128" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H128" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - TVS Diode</v>
@@ -10020,7 +10021,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:31">
+    <row r="129" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H129" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - MOVs</v>
@@ -10088,7 +10089,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:31">
+    <row r="130" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H130" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - GDT</v>
@@ -10156,7 +10157,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:31">
+    <row r="131" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H131" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Protection - Fuses</v>
@@ -10224,7 +10225,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:31">
+    <row r="132" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H132" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Screws</v>
@@ -10292,7 +10293,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:31">
+    <row r="133" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H133" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Mechanical  - Feet</v>
@@ -10360,7 +10361,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:31">
+    <row r="134" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H134" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>LEDs - Standard - Indicator - Through Hole</v>
@@ -10434,7 +10435,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:31">
+    <row r="135" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H135" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>LEDs - Standard - Indicator - SMD</v>
@@ -10508,7 +10509,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:31">
+    <row r="136" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H136" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Inductors - Ferrite Bead</v>
@@ -10576,7 +10577,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:31">
+    <row r="137" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H137" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Inductors</v>
@@ -10641,7 +10642,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:31">
+    <row r="138" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H138" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Linear Regulation</v>
@@ -10712,7 +10713,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:31">
+    <row r="139" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H139" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Power - Ideal Diodes</v>
@@ -10783,7 +10784,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:31">
+    <row r="140" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H140" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Embedded - MCU - Module</v>
@@ -10857,7 +10858,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:31">
+    <row r="141" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H141" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Embedded - MCU</v>
@@ -10928,7 +10929,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:31">
+    <row r="142" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H142" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>ICs - Analog - OP Amp</v>
@@ -10999,7 +11000,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:31">
+    <row r="143" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H143" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Transistors - BJT - NPN</v>
@@ -11073,7 +11074,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:31">
+    <row r="144" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H144" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Discreet - Diodes - Schottky</v>
@@ -11144,7 +11145,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:31">
+    <row r="145" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H145" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - USB</v>
@@ -11212,7 +11213,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:31">
+    <row r="146" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H146" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - RJ</v>
@@ -11280,7 +11281,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:31">
+    <row r="147" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H147" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Rectangular</v>
@@ -11348,7 +11349,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:31">
+    <row r="148" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H148" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Programming</v>
@@ -11416,7 +11417,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:31">
+    <row r="149" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H149" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Pads - Through Hole</v>
@@ -11487,7 +11488,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:31">
+    <row r="150" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H150" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Pads - SMD</v>
@@ -11558,7 +11559,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:31">
+    <row r="151" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H151" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Mezzanine</v>
@@ -11626,7 +11627,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:31">
+    <row r="152" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H152" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - IC socket</v>
@@ -11694,7 +11695,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="8:31">
+    <row r="153" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H153" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Connectors - Barrel Jack</v>
@@ -11762,7 +11763,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="8:31">
+    <row r="154" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H154" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - Oscillators  - Fixed - XO</v>
@@ -11836,7 +11837,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="8:31">
+    <row r="155" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H155" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Clock&amp;Timing - ICs - Generators &amp; Synthisizers</v>
@@ -11907,7 +11908,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="8:31">
+    <row r="156" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H156" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Capacitors - Unpolarized</v>
@@ -11975,7 +11976,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="8:31">
+    <row r="157" spans="8:31" x14ac:dyDescent="0.35">
       <c r="H157" t="str">
         <f>_xlfn.CONCAT(Table1[[#This Row],[Eff pt 1]:[Eff pt 7]])</f>
         <v>Cables - Premade</v>
